--- a/data/trans_dic/KIDM_A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,25</t>
+          <t>0,0; 29,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,17</t>
+          <t>0,0; 19,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 21,69</t>
+          <t>2,2; 21,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,54</t>
+          <t>0,0; 20,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 22,29</t>
+          <t>2,96; 20,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,54</t>
+          <t>0,0; 24,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 17,83</t>
+          <t>1,99; 17,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 15,54</t>
+          <t>2,91; 15,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 16,37</t>
+          <t>2,57; 15,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,17</t>
+          <t>1,39; 11,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,33</t>
+          <t>0,65; 5,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,37</t>
+          <t>0,27; 6,22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,17</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,76</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,87</t>
+          <t>0,0; 12,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 14,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 10,24</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,05</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,05</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,99</t>
+          <t>1,78; 15,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,29</t>
+          <t>2,31; 19,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,4</t>
+          <t>0,0; 17,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,12</t>
+          <t>1,25; 9,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,75</t>
+          <t>0,95; 8,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,61</t>
+          <t>1,54; 11,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 27,92</t>
+          <t>3,23; 27,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 30,92</t>
+          <t>3,47; 30,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,82</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,85</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,6</t>
+          <t>1,73; 15,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 19,79</t>
+          <t>3,32; 19,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,82</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,39</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>0,0; 10,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 10,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,96</t>
+          <t>0,73; 7,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 4,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,37</t>
+          <t>0,83; 8,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,0</t>
+          <t>0,82; 6,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,76</t>
+          <t>1,04; 5,81</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,9</t>
+          <t>0,99; 4,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,21</t>
+          <t>1,68; 5,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,95</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,17</t>
+          <t>0,32; 3,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,47</t>
+          <t>0,89; 3,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,77</t>
+          <t>2,16; 5,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,47</t>
+          <t>0,75; 3,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,0</t>
+          <t>0,37; 3,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,25</t>
+          <t>1,23; 3,21</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,84</t>
+          <t>2,28; 4,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,62</t>
+          <t>0,99; 2,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,4</t>
+          <t>0,56; 2,45</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2919</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4041</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4575</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>513; 5078</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4663</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>843; 5931</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6120</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>736; 6612</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1503; 8106</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1239; 7433</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2611</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>654; 5346</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3493</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6237</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2899</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3177</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>655; 5389</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4126</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>319; 7452</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3088</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4032</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3743</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3910</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2742</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4738</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2628</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5453</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>586; 5246</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>790; 6494</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6049</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>820; 6566</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>688; 6320</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1027; 7521</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2365</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2776</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3670</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>642; 5568</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>690; 6063</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2994</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3976</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>696; 6187</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1328; 7784</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3287</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 982</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3342</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3265</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4883</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3059</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3766</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3692</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4933</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3241</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>685; 6669</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5107</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3869</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4288</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>609; 5842</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2616</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3515</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>620; 5265</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 6375</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5359</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1552; 8639</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2646</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5430</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11382</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>20726</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2795; 11970</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4907; 15396</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2254; 9348</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>684; 6553</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2687; 10342</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>6736; 17923</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2453; 11722</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1015; 8430</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>7173; 18806</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>13781; 28689</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6434; 16695</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11845</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,47</t>
+          <t>0,0; 34,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,71</t>
+          <t>0,0; 21,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 21,78</t>
+          <t>2,27; 21,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,06</t>
+          <t>0,0; 20,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 20,83</t>
+          <t>2,39; 22,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,49</t>
+          <t>0,0; 23,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 17,89</t>
+          <t>2,0; 17,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 15,69</t>
+          <t>3,61; 17,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 15,39</t>
+          <t>2,79; 16,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,39</t>
+          <t>1,4; 11,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,38</t>
+          <t>0,65; 5,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,22</t>
+          <t>0,33; 5,51</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 14,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>0,0; 13,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,73</t>
+          <t>0,0; 14,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,24</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,17</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,98</t>
+          <t>1,82; 17,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 19,03</t>
+          <t>2,03; 19,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,38</t>
+          <t>0,0; 16,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,98</t>
+          <t>1,03; 9,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,74</t>
+          <t>1,14; 10,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,3</t>
+          <t>1,84; 11,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 27,99</t>
+          <t>3,21; 24,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 30,52</t>
+          <t>3,5; 31,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 18,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 22,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 15,35</t>
+          <t>1,78; 15,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 19,45</t>
+          <t>3,4; 19,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 11,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
     </row>
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 10,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,49</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,09</t>
+          <t>0,72; 6,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,42</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,08</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,0</t>
+          <t>0,83; 7,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,96</t>
+          <t>0,83; 6,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,81</t>
+          <t>1,0; 5,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,23</t>
+          <t>0,99; 3,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,27</t>
+          <t>1,87; 5,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,67; 2,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,1</t>
+          <t>0,35; 3,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,42</t>
+          <t>0,83; 3,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,74</t>
+          <t>2,28; 5,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,6</t>
+          <t>0,75; 3,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,09</t>
+          <t>0,38; 3,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,21</t>
+          <t>1,16; 3,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,75</t>
+          <t>2,22; 4,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,57</t>
+          <t>0,91; 2,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,45</t>
+          <t>0,55; 2,58</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 4679</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4575</t>
+          <t>0; 5008</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513; 5078</t>
+          <t>530; 5033</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4663</t>
+          <t>0; 4707</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>843; 5931</t>
+          <t>681; 6309</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6120</t>
+          <t>0; 5828</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>736; 6612</t>
+          <t>738; 6467</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1503; 8106</t>
+          <t>1866; 8810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1239; 7433</t>
+          <t>1347; 8063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2417,22 +2417,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2611</t>
+          <t>0; 2565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>654; 5346</t>
+          <t>655; 5447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3493</t>
+          <t>0; 3644</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6237</t>
+          <t>0; 5943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 4029</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>655; 5389</t>
+          <t>653; 5955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 4183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>319; 7452</t>
+          <t>390; 6600</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 3024</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 3995</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3743</t>
+          <t>0; 3792</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3910</t>
+          <t>0; 3876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2742</t>
+          <t>0; 4076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4738</t>
+          <t>0; 4939</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2264</t>
+          <t>0; 2695</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5453</t>
+          <t>0; 4699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>586; 5246</t>
+          <t>596; 5708</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>790; 6494</t>
+          <t>694; 6659</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6049</t>
+          <t>0; 5707</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>820; 6566</t>
+          <t>679; 6362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>688; 6320</t>
+          <t>827; 7283</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1027; 7521</t>
+          <t>1228; 7847</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>642; 5568</t>
+          <t>638; 4960</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>690; 6063</t>
+          <t>695; 6168</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2994</t>
+          <t>0; 3806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3976</t>
+          <t>0; 4565</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>696; 6187</t>
+          <t>716; 6407</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1328; 7784</t>
+          <t>1360; 7719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3287</t>
+          <t>0; 3261</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 982</t>
+          <t>0; 961</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3342</t>
+          <t>0; 3675</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>0; 965</t>
         </is>
       </c>
     </row>
@@ -3457,17 +3457,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3265</t>
+          <t>0; 2873</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4883</t>
+          <t>0; 4902</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3059</t>
+          <t>0; 3287</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3766</t>
+          <t>0; 3815</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3692</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4933</t>
+          <t>0; 3701</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3241</t>
+          <t>0; 3426</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>685; 6669</t>
+          <t>673; 5928</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 5107</t>
+          <t>0; 3956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 3645</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>609; 5842</t>
+          <t>604; 5323</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2616</t>
+          <t>0; 2617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>0; 3640</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>620; 5265</t>
+          <t>625; 5269</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 6375</t>
+          <t>0; 6126</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 5359</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1552; 8639</t>
+          <t>1488; 8528</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 3078</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 6326</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2795; 11970</t>
+          <t>2791; 11054</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4907; 15396</t>
+          <t>5479; 16503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2254; 9348</t>
+          <t>2156; 9219</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>684; 6553</t>
+          <t>743; 7180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2687; 10342</t>
+          <t>2507; 11529</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6736; 17923</t>
+          <t>7120; 17336</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2453; 11722</t>
+          <t>2438; 11252</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1015; 8430</t>
+          <t>1033; 9551</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7173; 18806</t>
+          <t>6774; 17910</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13781; 28689</t>
+          <t>13409; 28347</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6434; 16695</t>
+          <t>5896; 16314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2712; 11845</t>
+          <t>2673; 12489</t>
         </is>
       </c>
     </row>
